--- a/Project/mpt/Danh Sách Hàm Code.xlsx
+++ b/Project/mpt/Danh Sách Hàm Code.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\Cpp\tictactoe\Project\mpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDE873F-50A2-4316-9DA1-9219C8D92C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BA16A7-0F18-4D53-865F-CF4C8761B66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
   <si>
     <t>STT</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Đóng file log và giải phóng tài nguyên.</t>
+  </si>
+  <si>
+    <t>✅ Cần sửa lại</t>
   </si>
 </sst>
 </file>
@@ -270,7 +273,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,6 +283,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -316,6 +325,15 @@
       </extLst>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -995,17 +1013,17 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
+    <row r="23" spans="1:4" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="4" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1079,17 +1097,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
+    <row r="29" spans="1:4" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="C29" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>61</v>
       </c>
     </row>
